--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -5479,7 +5479,7 @@
         <v>120490417</v>
       </c>
       <c r="B43" t="n">
-        <v>4775</v>
+        <v>4777</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ75"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3842,54 +3842,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120635114</v>
+        <v>137168020</v>
       </c>
       <c r="B29" t="n">
-        <v>5178</v>
+        <v>57195</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102204</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Haddebo/Sjölunda, Nrk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>517596</v>
+        <v>516583</v>
       </c>
       <c r="R29" t="n">
-        <v>6536395</v>
+        <v>6535758</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3916,22 +3907,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Tjäder spillning på hygge</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3940,89 +3926,80 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635114</t>
+          <t>https://artportalen.se/Sighting/137168020</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134803960</v>
+        <v>120635114</v>
       </c>
       <c r="B30" t="n">
-        <v>45055</v>
+        <v>5178</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102021</v>
+        <v>102204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bavlinge, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519835</v>
+        <v>517596</v>
       </c>
       <c r="R30" t="n">
-        <v>6535070</v>
+        <v>6536395</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4046,22 +4023,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4077,24 +4054,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134803960</t>
+          <t>https://artportalen.se/Sighting/120635114</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134804509</v>
+        <v>134803960</v>
       </c>
       <c r="B31" t="n">
         <v>45055</v>
@@ -4149,10 +4126,10 @@
         <v>519835</v>
       </c>
       <c r="R31" t="n">
-        <v>6535071</v>
+        <v>6535070</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4207,27 +4184,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134804509</t>
+          <t>https://artportalen.se/Sighting/134803960</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134810115</v>
+        <v>134804509</v>
       </c>
       <c r="B32" t="n">
-        <v>43314</v>
+        <v>45055</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4235,21 +4212,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>201146</v>
+        <v>102021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4348,48 +4325,57 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134810115</t>
+          <t>https://artportalen.se/Sighting/134804509</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134804582</v>
+        <v>134810115</v>
       </c>
       <c r="B33" t="n">
-        <v>108205</v>
+        <v>43314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220083</v>
+        <v>201146</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4469,13 +4455,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134804582</t>
+          <t>https://artportalen.se/Sighting/134810115</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134806613</v>
+        <v>134804582</v>
       </c>
       <c r="B34" t="n">
         <v>108205</v>
@@ -4521,10 +4507,10 @@
         <v>519835</v>
       </c>
       <c r="R34" t="n">
-        <v>6535070</v>
+        <v>6535071</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,72 +4565,73 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134806613</t>
+          <t>https://artportalen.se/Sighting/134804582</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120490287</v>
+        <v>134806613</v>
       </c>
       <c r="B35" t="n">
-        <v>75428</v>
+        <v>108205</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>220083</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Molångsfallet, Nrk</t>
+          <t>Bavlinge, Nrk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518469</v>
+        <v>519835</v>
       </c>
       <c r="R35" t="n">
-        <v>6535004</v>
+        <v>6535070</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4668,12 +4655,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4689,24 +4686,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490287</t>
+          <t>https://artportalen.se/Sighting/134806613</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120490290</v>
+        <v>120490287</v>
       </c>
       <c r="B36" t="n">
         <v>75428</v>
@@ -4748,10 +4745,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518452</v>
+        <v>518469</v>
       </c>
       <c r="R36" t="n">
-        <v>6535003</v>
+        <v>6535004</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4810,13 +4807,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490290</t>
+          <t>https://artportalen.se/Sighting/120490287</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120490318</v>
+        <v>120490290</v>
       </c>
       <c r="B37" t="n">
         <v>75428</v>
@@ -4858,10 +4855,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518444</v>
+        <v>518452</v>
       </c>
       <c r="R37" t="n">
-        <v>6535002</v>
+        <v>6535003</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4920,13 +4917,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490318</t>
+          <t>https://artportalen.se/Sighting/120490290</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120490374</v>
+        <v>120490318</v>
       </c>
       <c r="B38" t="n">
         <v>75428</v>
@@ -4968,10 +4965,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518426</v>
+        <v>518444</v>
       </c>
       <c r="R38" t="n">
-        <v>6534998</v>
+        <v>6535002</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5030,38 +5027,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490374</t>
+          <t>https://artportalen.se/Sighting/120490318</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120490311</v>
+        <v>120490374</v>
       </c>
       <c r="B39" t="n">
-        <v>75300</v>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6428</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5078,10 +5075,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518448</v>
+        <v>518426</v>
       </c>
       <c r="R39" t="n">
-        <v>6535004</v>
+        <v>6534998</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5140,38 +5137,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490311</t>
+          <t>https://artportalen.se/Sighting/120490374</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120490404</v>
+        <v>120490311</v>
       </c>
       <c r="B40" t="n">
-        <v>79946</v>
+        <v>75300</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6428</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5184,14 +5181,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Molångsbergen, Nrk</t>
+          <t>Molångsfallet, Nrk</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518400</v>
+        <v>518448</v>
       </c>
       <c r="R40" t="n">
-        <v>6535136</v>
+        <v>6535004</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5250,13 +5247,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490404</t>
+          <t>https://artportalen.se/Sighting/120490311</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120490422</v>
+        <v>120490404</v>
       </c>
       <c r="B41" t="n">
         <v>79946</v>
@@ -5298,10 +5295,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518597</v>
+        <v>518400</v>
       </c>
       <c r="R41" t="n">
-        <v>6535166</v>
+        <v>6535136</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5360,38 +5357,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490422</t>
+          <t>https://artportalen.se/Sighting/120490404</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120490286</v>
+        <v>120490422</v>
       </c>
       <c r="B42" t="n">
-        <v>79583</v>
+        <v>79946</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6459</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5404,14 +5401,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Molångsfallet, Nrk</t>
+          <t>Molångsbergen, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518469</v>
+        <v>518597</v>
       </c>
       <c r="R42" t="n">
-        <v>6535004</v>
+        <v>6535166</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5470,16 +5467,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490286</t>
+          <t>https://artportalen.se/Sighting/120490422</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120490417</v>
+        <v>120490286</v>
       </c>
       <c r="B43" t="n">
-        <v>4777</v>
+        <v>79583</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5487,43 +5484,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100299</v>
+        <v>6459</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Molångsbergen, Nrk</t>
+          <t>Molångsfallet, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518449</v>
+        <v>518469</v>
       </c>
       <c r="R43" t="n">
-        <v>6535170</v>
+        <v>6535004</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5582,16 +5577,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490417</t>
+          <t>https://artportalen.se/Sighting/120490286</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120490336</v>
+        <v>120490417</v>
       </c>
       <c r="B44" t="n">
-        <v>5179</v>
+        <v>4777</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5599,21 +5594,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5628,14 +5623,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Molångsfallet, Nrk</t>
+          <t>Molångsbergen, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518436</v>
+        <v>518449</v>
       </c>
       <c r="R44" t="n">
-        <v>6535000</v>
+        <v>6535170</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5694,16 +5689,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490336</t>
+          <t>https://artportalen.se/Sighting/120490417</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120490321</v>
+        <v>120490336</v>
       </c>
       <c r="B45" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5711,21 +5706,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5734,7 +5729,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5744,10 +5739,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518445</v>
+        <v>518436</v>
       </c>
       <c r="R45" t="n">
-        <v>6535003</v>
+        <v>6535000</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5806,16 +5801,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490321</t>
+          <t>https://artportalen.se/Sighting/120490336</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104734918</v>
+        <v>120490321</v>
       </c>
       <c r="B46" t="n">
-        <v>8444</v>
+        <v>5199</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5823,21 +5818,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5852,14 +5847,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Molångsbergen, Fåglamossen-Bavlingebäcken, Nrk</t>
+          <t>Molångsfallet, Nrk</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518600</v>
+        <v>518445</v>
       </c>
       <c r="R46" t="n">
-        <v>6535166</v>
+        <v>6535003</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5886,12 +5881,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5918,13 +5913,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104734918</t>
+          <t>https://artportalen.se/Sighting/120490321</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104734973</v>
+        <v>104734918</v>
       </c>
       <c r="B47" t="n">
         <v>8444</v>
@@ -5968,10 +5963,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518493</v>
+        <v>518600</v>
       </c>
       <c r="R47" t="n">
-        <v>6535135</v>
+        <v>6535166</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6030,13 +6025,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104734973</t>
+          <t>https://artportalen.se/Sighting/104734918</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>104734987</v>
+        <v>104734973</v>
       </c>
       <c r="B48" t="n">
         <v>8444</v>
@@ -6080,10 +6075,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518564</v>
+        <v>518493</v>
       </c>
       <c r="R48" t="n">
-        <v>6535128</v>
+        <v>6535135</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6142,13 +6137,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104734987</t>
+          <t>https://artportalen.se/Sighting/104734973</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120490370</v>
+        <v>104734987</v>
       </c>
       <c r="B49" t="n">
         <v>8444</v>
@@ -6182,20 +6177,20 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Molångsfallet, Nrk</t>
+          <t>Molångsbergen, Fåglamossen-Bavlingebäcken, Nrk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518443</v>
+        <v>518564</v>
       </c>
       <c r="R49" t="n">
-        <v>6534984</v>
+        <v>6535128</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6222,12 +6217,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2022-11-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2022-11-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6254,16 +6249,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490370</t>
+          <t>https://artportalen.se/Sighting/104734987</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120490371</v>
+        <v>120490370</v>
       </c>
       <c r="B50" t="n">
-        <v>99035</v>
+        <v>8444</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6271,31 +6266,32 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6303,10 +6299,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518426</v>
+        <v>518443</v>
       </c>
       <c r="R50" t="n">
-        <v>6534993</v>
+        <v>6534984</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6365,16 +6361,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490371</t>
+          <t>https://artportalen.se/Sighting/120490370</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120490271</v>
+        <v>120490371</v>
       </c>
       <c r="B51" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6382,21 +6378,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6414,10 +6410,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518477</v>
+        <v>518426</v>
       </c>
       <c r="R51" t="n">
-        <v>6534997</v>
+        <v>6534993</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6476,16 +6472,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490271</t>
+          <t>https://artportalen.se/Sighting/120490371</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133676469</v>
+        <v>120490271</v>
       </c>
       <c r="B52" t="n">
-        <v>58061</v>
+        <v>97983</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6493,53 +6489,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102626</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hjärta, Nrk</t>
+          <t>Molångsfallet, Nrk</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>516431</v>
+        <v>518477</v>
       </c>
       <c r="R52" t="n">
-        <v>6534878</v>
+        <v>6534997</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6563,22 +6551,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6587,55 +6565,56 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133676469</t>
+          <t>https://artportalen.se/Sighting/120490271</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134223604</v>
+        <v>133676469</v>
       </c>
       <c r="B53" t="n">
-        <v>57386</v>
+        <v>58061</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102954</v>
+        <v>102626</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6644,7 +6623,11 @@
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -6687,22 +6670,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6728,33 +6711,33 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134223604</t>
+          <t>https://artportalen.se/Sighting/133676469</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134174906</v>
+        <v>134223604</v>
       </c>
       <c r="B54" t="n">
-        <v>58658</v>
+        <v>57386</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103044</v>
+        <v>102954</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6811,22 +6794,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6852,55 +6835,63 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134174906</t>
+          <t>https://artportalen.se/Sighting/134223604</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>62686291</v>
+        <v>134174906</v>
       </c>
       <c r="B55" t="n">
-        <v>107708</v>
+        <v>58658</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>245</v>
+        <v>103044</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ö:a Hjärta 6450/1750, Nrk</t>
+          <t>Hjärta, Nrk</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>518089</v>
+        <v>516431</v>
       </c>
       <c r="R55" t="n">
-        <v>6534405</v>
+        <v>6534878</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6927,17 +6918,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>1980-07-10</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>1980-07-10</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>9 ex. 2016 ej återfunnen. Biotopen oigenkännlig</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6948,74 +6944,73 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Ej återfunnen 2016. Biotopen sannolikt alltför förändrad</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62686291</t>
+          <t>https://artportalen.se/Sighting/134174906</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>85451223</v>
+        <v>62686291</v>
       </c>
       <c r="B56" t="n">
-        <v>80367</v>
+        <v>107708</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6457</v>
+        <v>245</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>väst Hjärtaviken, Nrk</t>
+          <t>Ö:a Hjärta 6450/1750, Nrk</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>517772</v>
+        <v>518089</v>
       </c>
       <c r="R56" t="n">
-        <v>6533805</v>
+        <v>6534405</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7039,12 +7034,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>1980-07-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>1980-07-10</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>9 ex. 2016 ej återfunnen. Biotopen oigenkännlig</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7055,31 +7055,36 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Ej återfunnen 2016. Biotopen sannolikt alltför förändrad</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451223</t>
+          <t>https://artportalen.se/Sighting/62686291</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>78430052</v>
+        <v>85451223</v>
       </c>
       <c r="B57" t="n">
-        <v>96348</v>
+        <v>80367</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7087,37 +7092,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2810</v>
+        <v>6457</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Charlottendal, Nrk</t>
+          <t>väst Hjärtaviken, Nrk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518424</v>
+        <v>517772</v>
       </c>
       <c r="R57" t="n">
-        <v>6533707</v>
+        <v>6533805</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7141,12 +7146,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2019-06-15</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2019-06-15</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7161,27 +7166,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78430052</t>
+          <t>https://artportalen.se/Sighting/85451223</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>54014137</v>
+        <v>78430052</v>
       </c>
       <c r="B58" t="n">
-        <v>91872</v>
+        <v>96348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7189,34 +7194,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>2810</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>Charlottendal, Nrk</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518326</v>
+        <v>518424</v>
       </c>
       <c r="R58" t="n">
-        <v>6533577</v>
+        <v>6533707</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7243,12 +7248,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-06-15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-06-15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7263,65 +7268,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54014137</t>
+          <t>https://artportalen.se/Sighting/78430052</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>85451486</v>
+        <v>54014137</v>
       </c>
       <c r="B59" t="n">
-        <v>92205</v>
+        <v>91872</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>73</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Baggesand, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518702</v>
+        <v>518326</v>
       </c>
       <c r="R59" t="n">
-        <v>6533363</v>
+        <v>6533577</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7345,12 +7350,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7365,27 +7370,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451486</t>
+          <t>https://artportalen.se/Sighting/54014137</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>80563834</v>
+        <v>85451486</v>
       </c>
       <c r="B60" t="n">
-        <v>91909</v>
+        <v>92205</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7393,37 +7398,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>73</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>Baggesand, Nrk</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518862</v>
+        <v>518702</v>
       </c>
       <c r="R60" t="n">
-        <v>6532925</v>
+        <v>6533363</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7447,12 +7452,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7463,33 +7468,28 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>låga av gran</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563834</t>
+          <t>https://artportalen.se/Sighting/85451486</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>85451487</v>
+        <v>80563834</v>
       </c>
       <c r="B61" t="n">
         <v>91909</v>
@@ -7520,17 +7520,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Baggesand, Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518897</v>
+        <v>518862</v>
       </c>
       <c r="R61" t="n">
-        <v>6532914</v>
+        <v>6532925</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7570,28 +7570,33 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>låga av gran</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451487</t>
+          <t>https://artportalen.se/Sighting/80563834</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>85451488</v>
+        <v>85451487</v>
       </c>
       <c r="B62" t="n">
         <v>91909</v>
@@ -7626,10 +7631,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518856</v>
+        <v>518897</v>
       </c>
       <c r="R62" t="n">
-        <v>6532925</v>
+        <v>6532914</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7687,57 +7692,51 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451488</t>
+          <t>https://artportalen.se/Sighting/85451487</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>55322405</v>
+        <v>85451488</v>
       </c>
       <c r="B63" t="n">
-        <v>91966</v>
+        <v>91909</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5321</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Baggesand, Nrk</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518957</v>
+        <v>518856</v>
       </c>
       <c r="R63" t="n">
-        <v>6533260</v>
+        <v>6532925</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7764,12 +7763,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7778,31 +7777,30 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55322405</t>
+          <t>https://artportalen.se/Sighting/85451488</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>98101330</v>
+        <v>55322405</v>
       </c>
       <c r="B64" t="n">
         <v>91966</v>
@@ -7830,27 +7828,26 @@
           <t>(Fr.) Ryvarden</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>N Baggesandstjärnen, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518968</v>
+        <v>518957</v>
       </c>
       <c r="R64" t="n">
-        <v>6533243</v>
+        <v>6533260</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7874,22 +7871,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7905,27 +7892,27 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98101330</t>
+          <t>https://artportalen.se/Sighting/55322405</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>85451507</v>
+        <v>98101330</v>
       </c>
       <c r="B65" t="n">
-        <v>79707</v>
+        <v>91966</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7933,37 +7920,44 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6431</v>
+        <v>5321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Baggesand, Nrk</t>
+          <t>N Baggesandstjärnen, Nrk</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518735</v>
+        <v>518968</v>
       </c>
       <c r="R65" t="n">
-        <v>6533098</v>
+        <v>6533243</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7987,12 +7981,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2022-01-13</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2022-01-13</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8001,55 +8005,56 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451507</t>
+          <t>https://artportalen.se/Sighting/98101330</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>85451509</v>
+        <v>85451507</v>
       </c>
       <c r="B66" t="n">
-        <v>79084</v>
+        <v>79707</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6431</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8059,10 +8064,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518825</v>
+        <v>518735</v>
       </c>
       <c r="R66" t="n">
-        <v>6533312</v>
+        <v>6533098</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8120,16 +8125,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451509</t>
+          <t>https://artportalen.se/Sighting/85451507</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>85451483</v>
+        <v>85451509</v>
       </c>
       <c r="B67" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8137,21 +8142,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8161,10 +8166,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518829</v>
+        <v>518825</v>
       </c>
       <c r="R67" t="n">
-        <v>6533317</v>
+        <v>6533312</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8222,38 +8227,38 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451483</t>
+          <t>https://artportalen.se/Sighting/85451509</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>85451531</v>
+        <v>85451483</v>
       </c>
       <c r="B68" t="n">
-        <v>80367</v>
+        <v>79946</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6457</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8263,10 +8268,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518726</v>
+        <v>518829</v>
       </c>
       <c r="R68" t="n">
-        <v>6533324</v>
+        <v>6533317</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8324,13 +8329,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451531</t>
+          <t>https://artportalen.se/Sighting/85451483</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>85451532</v>
+        <v>85451531</v>
       </c>
       <c r="B69" t="n">
         <v>80367</v>
@@ -8365,10 +8370,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518706</v>
+        <v>518726</v>
       </c>
       <c r="R69" t="n">
-        <v>6533361</v>
+        <v>6533324</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8426,16 +8431,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451532</t>
+          <t>https://artportalen.se/Sighting/85451531</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119730876</v>
+        <v>85451532</v>
       </c>
       <c r="B70" t="n">
-        <v>57899</v>
+        <v>80367</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8443,45 +8448,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100067</v>
+        <v>6457</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Baggesand, Nrk</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518873</v>
+        <v>518706</v>
       </c>
       <c r="R70" t="n">
-        <v>6533167</v>
+        <v>6533361</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8505,12 +8502,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8525,27 +8522,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119730876</t>
+          <t>https://artportalen.se/Sighting/85451532</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>80563835</v>
+        <v>119730876</v>
       </c>
       <c r="B71" t="n">
-        <v>5179</v>
+        <v>57899</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8553,37 +8550,45 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>100067</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>Baggesand, Nrk</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518851</v>
+        <v>518873</v>
       </c>
       <c r="R71" t="n">
-        <v>6532925</v>
+        <v>6533167</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8607,12 +8612,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8623,83 +8628,66 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563835</t>
+          <t>https://artportalen.se/Sighting/119730876</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>79351146</v>
+        <v>80563835</v>
       </c>
       <c r="B72" t="n">
-        <v>58497</v>
+        <v>5179</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102990</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Baggesandtärnen, väster om., Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518745</v>
+        <v>518851</v>
       </c>
       <c r="R72" t="n">
-        <v>6533090</v>
+        <v>6532925</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8726,22 +8714,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2019-04-25</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2019-04-25</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8752,48 +8730,53 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79351146</t>
+          <t>https://artportalen.se/Sighting/80563835</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>79351057</v>
+        <v>79351146</v>
       </c>
       <c r="B73" t="n">
-        <v>58327</v>
+        <v>58497</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8816,14 +8799,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Baggesandtärnen, Nrk</t>
+          <t>Baggesandtärnen, väster om., Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518755</v>
+        <v>518745</v>
       </c>
       <c r="R73" t="n">
-        <v>6532980</v>
+        <v>6533090</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8891,38 +8874,38 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79351057</t>
+          <t>https://artportalen.se/Sighting/79351146</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>90856737</v>
+        <v>79351057</v>
       </c>
       <c r="B74" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8934,23 +8917,23 @@
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Baggesand Ö om, Nrk</t>
+          <t>Baggesandtärnen, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518881</v>
+        <v>518755</v>
       </c>
       <c r="R74" t="n">
-        <v>6533297</v>
+        <v>6532980</v>
       </c>
       <c r="S74" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8974,12 +8957,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-02-12</t>
+          <t>2019-04-25</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-02-12</t>
+          <t>2019-04-25</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8994,49 +8987,49 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90856737</t>
+          <t>https://artportalen.se/Sighting/79351057</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>55322391</v>
+        <v>90856737</v>
       </c>
       <c r="B75" t="n">
-        <v>101326</v>
+        <v>58114</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9044,22 +9037,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Baggesand Ö om, Nrk</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518981</v>
+        <v>518881</v>
       </c>
       <c r="R75" t="n">
-        <v>6533359</v>
+        <v>6533297</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9083,12 +9081,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2021-02-12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2021-02-12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9103,16 +9101,125 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90856737</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>55322391</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>518981</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6533359</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2014-09-14</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2014-09-14</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Viktor Säfve</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Viktor Säfve</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/55322391</t>
         </is>
@@ -9194,6 +9301,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>137168020</v>
       </c>
       <c r="B29" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>137168020</v>
       </c>
       <c r="B29" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -5615,11 +5615,7 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>137168020</v>
       </c>
       <c r="B29" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>120490417</v>
       </c>
       <c r="B44" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>137168020</v>
       </c>
       <c r="B29" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>137168020</v>
       </c>
       <c r="B29" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
